--- a/tabelas/FT_ISAGRUPCOBETURA.xlsx
+++ b/tabelas/FT_ISAGRUPCOBETURA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3f4ef99f068508f/STANG/5.MotorCalculo/MotorTransporteV2/tabelas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/99477d7318b1e097/14. Gisele^0Jardel/Atuá Estratégia ^0 Análises/8. Projetos/STANG/5.MotorCalculo/01_RC_Ambiental/MotorTransporteV5/tabelas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{49071044-2EED-482C-AECD-3E07F6FE59DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C652525D-86A0-4A68-B80F-0D34435A4C0E}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="13_ncr:1_{49071044-2EED-482C-AECD-3E07F6FE59DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{615DE2CA-0BAF-4936-B5A9-020C3B497DAA}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{77FAD20C-44E5-4827-8893-D4E5A201625A}"/>
   </bookViews>
@@ -588,8 +588,9 @@
     <col min="3" max="3" width="23.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.33203125" style="9" customWidth="1"/>
     <col min="5" max="5" width="13.21875" style="9" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="17" width="9.44140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" style="10" customWidth="1"/>
+    <col min="7" max="12" width="9.44140625" style="10" customWidth="1"/>
+    <col min="13" max="17" width="9.44140625" style="10" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9.5546875" style="4" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13.6640625" style="4" bestFit="1" customWidth="1"/>
     <col min="20" max="16384" width="8.88671875" style="2"/>
@@ -695,16 +696,16 @@
         <v>1.05</v>
       </c>
       <c r="N2" s="11">
-        <v>0.8</v>
+        <v>0.76190476190476186</v>
       </c>
       <c r="O2" s="11">
-        <v>0.9</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="P2" s="11">
-        <v>0.95</v>
+        <v>0.80952380952380953</v>
       </c>
       <c r="Q2" s="11">
-        <v>0.95</v>
+        <v>0.80952380952380953</v>
       </c>
       <c r="R2" s="5">
         <v>1000</v>
@@ -752,19 +753,19 @@
         <v>1</v>
       </c>
       <c r="M3" s="11">
-        <v>1.1680999999999999</v>
+        <v>1.0813600000000001</v>
       </c>
       <c r="N3" s="11">
-        <v>1.1680999999999999</v>
+        <v>1.0802138048383516</v>
       </c>
       <c r="O3" s="11">
-        <v>1.0681</v>
+        <v>0.98773766368276983</v>
       </c>
       <c r="P3" s="11">
-        <v>1</v>
+        <v>0.98971313901013536</v>
       </c>
       <c r="Q3" s="11">
-        <v>1.0049999999999999</v>
+        <v>1.0192215358437524</v>
       </c>
       <c r="R3" s="5">
         <v>1000</v>
@@ -812,19 +813,19 @@
         <v>1</v>
       </c>
       <c r="M4" s="11">
-        <v>1.2862</v>
+        <v>1.1127199999999999</v>
       </c>
       <c r="N4" s="11">
-        <v>1.1865000000000001</v>
+        <v>1.0663059889280324</v>
       </c>
       <c r="O4" s="11">
-        <v>1.1861999999999999</v>
+        <v>1.0660363793227408</v>
       </c>
       <c r="P4" s="11">
-        <v>1.1000000000000001</v>
+        <v>1.0681684520813861</v>
       </c>
       <c r="Q4" s="11">
-        <v>1.0315799999999999</v>
+        <v>1.0668369401107198</v>
       </c>
       <c r="R4" s="5">
         <v>1000</v>
@@ -872,19 +873,19 @@
         <v>1</v>
       </c>
       <c r="M5" s="11">
-        <v>1.4043000000000001</v>
+        <v>1.14408</v>
       </c>
       <c r="N5" s="11">
-        <v>1.4043000000000001</v>
+        <v>1.2274491294315084</v>
       </c>
       <c r="O5" s="11">
-        <v>1.3043</v>
+        <v>1.140042654359835</v>
       </c>
       <c r="P5" s="11">
-        <v>1.1100000000000001</v>
+        <v>1.1423227396685547</v>
       </c>
       <c r="Q5" s="11">
-        <v>1.0518799999999999</v>
+        <v>1.1699381744866326</v>
       </c>
       <c r="R5" s="5">
         <v>1000</v>
@@ -932,19 +933,19 @@
         <v>1</v>
       </c>
       <c r="M6" s="11">
-        <v>1.5224</v>
+        <v>1.17544</v>
       </c>
       <c r="N6" s="11">
-        <v>1.5224</v>
+        <v>1.295174572925883</v>
       </c>
       <c r="O6" s="11">
-        <v>1.4224000000000001</v>
+        <v>1.2101000476417343</v>
       </c>
       <c r="P6" s="11">
-        <v>1.4224000000000001</v>
+        <v>1.2125202477370178</v>
       </c>
       <c r="Q6" s="11">
-        <v>1.0622400000000001</v>
+        <v>1.2392649561015452</v>
       </c>
       <c r="R6" s="5">
         <v>1000</v>
@@ -992,19 +993,19 @@
         <v>1</v>
       </c>
       <c r="M7" s="11">
-        <v>1.6405000000000001</v>
+        <v>1.2068000000000001</v>
       </c>
       <c r="N7" s="11">
-        <v>1.6405000000000001</v>
+        <v>1.3593801789857474</v>
       </c>
       <c r="O7" s="11">
-        <v>1.5405</v>
+        <v>1.2765164070268478</v>
       </c>
       <c r="P7" s="11">
-        <v>1.6405000000000001</v>
+        <v>1.2790694398409015</v>
       </c>
       <c r="Q7" s="11">
-        <v>1.08405</v>
+        <v>1.304988675284499</v>
       </c>
       <c r="R7" s="5">
         <v>1000</v>
@@ -1052,19 +1053,19 @@
         <v>1</v>
       </c>
       <c r="M8" s="11">
-        <v>1.9085999999999999</v>
+        <v>1.2381599999999999</v>
       </c>
       <c r="N8" s="11">
-        <v>1.7585999999999999</v>
+        <v>1.4203333979453383</v>
       </c>
       <c r="O8" s="11">
-        <v>1.6586000000000001</v>
+        <v>1.3395683918071979</v>
       </c>
       <c r="P8" s="11">
-        <v>1.7585999999999999</v>
+        <v>1.3422475285908122</v>
       </c>
       <c r="Q8" s="11">
-        <v>1.0958600000000001</v>
+        <v>1.3673831061144497</v>
       </c>
       <c r="R8" s="5">
         <v>1000</v>
@@ -1112,19 +1113,19 @@
         <v>1</v>
       </c>
       <c r="M9" s="11">
-        <v>2.0266999999999999</v>
+        <v>1.26952</v>
       </c>
       <c r="N9" s="11">
-        <v>1.8767</v>
+        <v>1.4782752536391708</v>
       </c>
       <c r="O9" s="11">
-        <v>1.7766999999999999</v>
+        <v>1.3995053248471863</v>
       </c>
       <c r="P9" s="11">
-        <v>1.8767</v>
+        <v>1.4023043354968807</v>
       </c>
       <c r="Q9" s="11">
-        <v>1.18767</v>
+        <v>1.4266949713277459</v>
       </c>
       <c r="R9" s="5">
         <v>1000</v>
@@ -1172,19 +1173,19 @@
         <v>1</v>
       </c>
       <c r="M10" s="11">
-        <v>2.1448</v>
+        <v>1.30088</v>
       </c>
       <c r="N10" s="11">
-        <v>1.9947999999999999</v>
+        <v>1.5334235286882725</v>
       </c>
       <c r="O10" s="11">
-        <v>1.9947999999999999</v>
+        <v>1.5334235286882725</v>
       </c>
       <c r="P10" s="11">
-        <v>1.9947999999999999</v>
+        <v>1.536490375745649</v>
       </c>
       <c r="Q10" s="11">
-        <v>1.1348</v>
+        <v>1.5344458110407313</v>
       </c>
       <c r="R10" s="5">
         <v>1000</v>
@@ -1232,19 +1233,19 @@
         <v>1</v>
       </c>
       <c r="M11" s="11">
-        <v>2.2628999999999997</v>
+        <v>1.3322400000000001</v>
       </c>
       <c r="N11" s="11">
-        <v>2.2128999999999999</v>
+        <v>1.6610370503813126</v>
       </c>
       <c r="O11" s="11">
-        <v>2.1128999999999998</v>
+        <v>1.5859754999099258</v>
       </c>
       <c r="P11" s="11">
-        <v>2.2128999999999999</v>
+        <v>1.5891474509097456</v>
       </c>
       <c r="Q11" s="11">
-        <v>1.1629</v>
+        <v>1.6120533337336613</v>
       </c>
       <c r="R11" s="5">
         <v>1000</v>
@@ -1292,19 +1293,19 @@
         <v>1</v>
       </c>
       <c r="M12" s="11">
-        <v>2.3809999999999998</v>
+        <v>1.3635999999999999</v>
       </c>
       <c r="N12" s="11">
-        <v>2.431</v>
+        <v>1.7827808741566442</v>
       </c>
       <c r="O12" s="11">
-        <v>2.331</v>
+        <v>1.637650337342329</v>
       </c>
       <c r="P12" s="11">
-        <v>2.331</v>
+        <v>1.6409256380170139</v>
       </c>
       <c r="Q12" s="11">
-        <v>1.1829000000000001</v>
+        <v>1.6871189498386625</v>
       </c>
       <c r="R12" s="5">
         <v>1000</v>
@@ -1352,19 +1353,19 @@
         <v>1</v>
       </c>
       <c r="M13" s="11">
-        <v>2.4990999999999999</v>
+        <v>1.39496</v>
       </c>
       <c r="N13" s="11">
-        <v>2.6490999999999998</v>
+        <v>1.8990508688421173</v>
       </c>
       <c r="O13" s="11">
-        <v>2.5491000000000001</v>
+        <v>1.6839909388082812</v>
       </c>
       <c r="P13" s="11">
-        <v>2.4491000000000001</v>
+        <v>1.6873589206858979</v>
       </c>
       <c r="Q13" s="11">
-        <v>1.2082900000000001</v>
+        <v>1.7568002427787652</v>
       </c>
       <c r="R13" s="5">
         <v>1000</v>
@@ -1412,19 +1413,19 @@
         <v>1</v>
       </c>
       <c r="M14" s="11">
-        <v>2.6172</v>
+        <v>1.42632</v>
       </c>
       <c r="N14" s="11">
-        <v>2.7671999999999999</v>
+        <v>1.9400975938078411</v>
       </c>
       <c r="O14" s="11">
-        <v>2.6671999999999998</v>
+        <v>1.729766111391553</v>
       </c>
       <c r="P14" s="11">
-        <v>2.5672000000000001</v>
+        <v>1.7332256436143361</v>
       </c>
       <c r="Q14" s="11">
-        <v>1.2382899999999999</v>
+        <v>1.8010297829379101</v>
       </c>
       <c r="R14" s="5">
         <v>1000</v>
@@ -1472,19 +1473,19 @@
         <v>1</v>
       </c>
       <c r="M15" s="11">
-        <v>2.9853000000000001</v>
+        <v>1.45777</v>
       </c>
       <c r="N15" s="11">
-        <v>2.8853</v>
+        <v>1.9792559868840762</v>
       </c>
       <c r="O15" s="11">
-        <v>2.7829999999999999</v>
+        <v>1.7734622059721357</v>
       </c>
       <c r="P15" s="11">
-        <v>2.6852999999999998</v>
+        <v>1.7770091303840798</v>
       </c>
       <c r="Q15" s="11">
-        <v>1.2582899999999999</v>
+        <v>1.8432424410800974</v>
       </c>
       <c r="R15" s="5">
         <v>1000</v>
